--- a/Data Master Karyawan.xlsx
+++ b/Data Master Karyawan.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Al Ghiffari\HR ANALYST - Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E97F7B0-59E9-40BA-A344-80E1C36BAF10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D17730FF-6EA3-42F7-A84E-4F4D9168B26E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master ID" sheetId="1" r:id="rId1"/>
-    <sheet name="Kode Cabang" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="Kode Cabang" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Master ID'!$A$1:$K$181</definedName>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="721">
   <si>
     <t>ID Karyawan</t>
   </si>
@@ -1999,16 +2000,218 @@
   </si>
   <si>
     <t>3207180204780013</t>
+  </si>
+  <si>
+    <t>Nama Tenaga Kerja</t>
+  </si>
+  <si>
+    <t>Perusahaan</t>
+  </si>
+  <si>
+    <t>Potongan BPJS Kesehatan</t>
+  </si>
+  <si>
+    <t>Potongan BPJS TK</t>
+  </si>
+  <si>
+    <t>AAN TURIPNO</t>
+  </si>
+  <si>
+    <t>PT. JIP</t>
+  </si>
+  <si>
+    <t>AAT AHMAD HIDAYAT</t>
+  </si>
+  <si>
+    <t>AMRULLAH</t>
+  </si>
+  <si>
+    <t>ANDI SANTANU</t>
+  </si>
+  <si>
+    <t>BAYU TRI ANGGORO</t>
+  </si>
+  <si>
+    <t>BIANINGRUM</t>
+  </si>
+  <si>
+    <t>BRIANN JONATHAN EDISANTO</t>
+  </si>
+  <si>
+    <t>DAFFA MARCEL ALFARRAS</t>
+  </si>
+  <si>
+    <t>EGI PERMANA</t>
+  </si>
+  <si>
+    <t>ERI MUTAQIN</t>
+  </si>
+  <si>
+    <t>FAHRUL AZI</t>
+  </si>
+  <si>
+    <t>FIQRI AMIRULLOH MAULIDAN</t>
+  </si>
+  <si>
+    <t>HAMDANI</t>
+  </si>
+  <si>
+    <t>HARYANTO SE</t>
+  </si>
+  <si>
+    <t>ISTIROPAH</t>
+  </si>
+  <si>
+    <t>IVO TANDHI</t>
+  </si>
+  <si>
+    <t>IWA KARTIWA</t>
+  </si>
+  <si>
+    <t>IWAN SETIAWAN</t>
+  </si>
+  <si>
+    <t>KUSNADI</t>
+  </si>
+  <si>
+    <t>M FARHAN RAMDHANI</t>
+  </si>
+  <si>
+    <t>MELLA HARYATI</t>
+  </si>
+  <si>
+    <t>MUCHTAR KUSMAYADI</t>
+  </si>
+  <si>
+    <t>MUHAMAD HOPID</t>
+  </si>
+  <si>
+    <t>MUHAMAD IMRON SOPARY</t>
+  </si>
+  <si>
+    <t>MUHAMMAD IHSAN ISWAHYUDHI</t>
+  </si>
+  <si>
+    <t>NADIA DWI LIA ANDRIANI</t>
+  </si>
+  <si>
+    <t>NOVAL HANDIKA</t>
+  </si>
+  <si>
+    <t>NUR OCTAVIANI</t>
+  </si>
+  <si>
+    <t>PANDU GALIH PRAKOSO</t>
+  </si>
+  <si>
+    <t>RAHMAN ZAENAL HASBULLAH</t>
+  </si>
+  <si>
+    <t>RISA SRINITA</t>
+  </si>
+  <si>
+    <t>RIYAN SETIAWAN</t>
+  </si>
+  <si>
+    <t>SAPTO FAMA</t>
+  </si>
+  <si>
+    <t>SAMAWI</t>
+  </si>
+  <si>
+    <t>SUCI RAHMAWATI</t>
+  </si>
+  <si>
+    <t>TAOPIK HIDAYAT</t>
+  </si>
+  <si>
+    <t>YUDITH AFIDAH ALANUARI</t>
+  </si>
+  <si>
+    <t>YUSTARI ANGGRAENI</t>
+  </si>
+  <si>
+    <t>DEDI CAHYANTO</t>
+  </si>
+  <si>
+    <t>CV. JAI</t>
+  </si>
+  <si>
+    <t>DIKI KUSMAYADI</t>
+  </si>
+  <si>
+    <t>DITA SEPTIANTI</t>
+  </si>
+  <si>
+    <t>EDI KUSWANTO</t>
+  </si>
+  <si>
+    <t>FATURRACHMAN</t>
+  </si>
+  <si>
+    <t>HADID PERMANI</t>
+  </si>
+  <si>
+    <t>HARRY</t>
+  </si>
+  <si>
+    <t>HERU YANUARTO</t>
+  </si>
+  <si>
+    <t>KHEIRIL HAQ</t>
+  </si>
+  <si>
+    <t>MUHAMMAD JULIANA AKBAR</t>
+  </si>
+  <si>
+    <t>NABILA WARDAH SAADAH</t>
+  </si>
+  <si>
+    <t>NURYONO</t>
+  </si>
+  <si>
+    <t>REALITA</t>
+  </si>
+  <si>
+    <t>SHELLA SEPTIYADIS</t>
+  </si>
+  <si>
+    <t>SRI FUJI ASTUTI</t>
+  </si>
+  <si>
+    <t>SUPAN</t>
+  </si>
+  <si>
+    <t>TOMI GUNAWAN</t>
+  </si>
+  <si>
+    <t>TRI KARTIKA SIREGAR</t>
+  </si>
+  <si>
+    <t>TRI SARASWATI</t>
+  </si>
+  <si>
+    <t>YULITA FAJARINI</t>
+  </si>
+  <si>
+    <t>BPJS Kesehatan</t>
+  </si>
+  <si>
+    <t>BPJS TK</t>
+  </si>
+  <si>
+    <t>ada</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2027,8 +2230,29 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="0" tint="-4.9989318521683403E-2"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2040,8 +2264,13 @@
         <fgColor rgb="FF305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00BF00"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2049,17 +2278,93 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2362,7 +2667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K181"/>
+  <dimension ref="A1:M181"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2375,9 +2680,11 @@
     <col min="8" max="8" width="22" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
     <col min="10" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2411,8 +2718,14 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -2444,8 +2757,14 @@
       <c r="K2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L2" s="7">
+        <v>76750</v>
+      </c>
+      <c r="M2" s="11">
+        <v>230250</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>19</v>
       </c>
@@ -2477,8 +2796,14 @@
       <c r="K3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L3" s="11">
+        <v>63500</v>
+      </c>
+      <c r="M3" s="11">
+        <v>190500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>23</v>
       </c>
@@ -2512,8 +2837,10 @@
       <c r="K4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
@@ -2547,8 +2874,14 @@
       <c r="K5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L5" s="11">
+        <v>53994</v>
+      </c>
+      <c r="M5" s="11">
+        <v>161982</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>31</v>
       </c>
@@ -2582,8 +2915,10 @@
       <c r="K6" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>35</v>
       </c>
@@ -2617,8 +2952,10 @@
       <c r="K7" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>39</v>
       </c>
@@ -2652,8 +2989,14 @@
       <c r="K8" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L8" s="11">
+        <v>53994</v>
+      </c>
+      <c r="M8" s="11">
+        <v>161982</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>43</v>
       </c>
@@ -2687,8 +3030,14 @@
       <c r="K9" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L9" s="11">
+        <v>55550</v>
+      </c>
+      <c r="M9" s="11">
+        <v>166650</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>47</v>
       </c>
@@ -2722,8 +3071,14 @@
       <c r="K10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L10" s="11">
+        <v>53994</v>
+      </c>
+      <c r="M10" s="11">
+        <v>161982</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>51</v>
       </c>
@@ -2757,8 +3112,14 @@
       <c r="K11" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L11" s="11">
+        <v>56300</v>
+      </c>
+      <c r="M11" s="11">
+        <v>168900</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>55</v>
       </c>
@@ -2792,8 +3153,10 @@
       <c r="K12" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>60</v>
       </c>
@@ -2824,8 +3187,10 @@
       <c r="J13" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>64</v>
       </c>
@@ -2859,8 +3224,14 @@
       <c r="K14" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L14" s="11">
+        <v>76000</v>
+      </c>
+      <c r="M14" s="11">
+        <v>228000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>69</v>
       </c>
@@ -2894,8 +3265,14 @@
       <c r="K15" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L15" s="11">
+        <v>64900</v>
+      </c>
+      <c r="M15" s="11">
+        <v>194700</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>74</v>
       </c>
@@ -2929,8 +3306,14 @@
       <c r="K16" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L16" s="11">
+        <v>66300</v>
+      </c>
+      <c r="M16" s="11">
+        <v>198900</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>78</v>
       </c>
@@ -2962,8 +3345,10 @@
       <c r="K17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>82</v>
       </c>
@@ -2995,8 +3380,14 @@
       <c r="K18" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L18" s="11">
+        <v>54700</v>
+      </c>
+      <c r="M18" s="11">
+        <v>164100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>86</v>
       </c>
@@ -3028,8 +3419,14 @@
       <c r="K19" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L19" s="11">
+        <v>80000</v>
+      </c>
+      <c r="M19" s="11">
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>92</v>
       </c>
@@ -3061,8 +3458,14 @@
       <c r="K20" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L20" s="11">
+        <v>80000</v>
+      </c>
+      <c r="M20" s="11">
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>96</v>
       </c>
@@ -3094,8 +3497,14 @@
       <c r="K21" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L21" s="11">
+        <v>72000</v>
+      </c>
+      <c r="M21" s="11">
+        <v>216000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>101</v>
       </c>
@@ -3127,8 +3536,14 @@
       <c r="K22" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L22" s="11">
+        <v>65000</v>
+      </c>
+      <c r="M22" s="11">
+        <v>195000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>105</v>
       </c>
@@ -3158,8 +3573,10 @@
       <c r="K23" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>108</v>
       </c>
@@ -3189,8 +3606,10 @@
       <c r="K24" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>111</v>
       </c>
@@ -3220,8 +3639,10 @@
       <c r="K25" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>114</v>
       </c>
@@ -3253,8 +3674,14 @@
       <c r="K26" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L26" s="11">
+        <v>90000</v>
+      </c>
+      <c r="M26" s="11">
+        <v>270000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>118</v>
       </c>
@@ -3284,8 +3711,10 @@
       <c r="K27" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>121</v>
       </c>
@@ -3319,8 +3748,10 @@
       <c r="K28" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>126</v>
       </c>
@@ -3354,8 +3785,10 @@
       <c r="K29" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>131</v>
       </c>
@@ -3389,8 +3822,10 @@
       <c r="K30" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>135</v>
       </c>
@@ -3424,8 +3859,10 @@
       <c r="K31" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>139</v>
       </c>
@@ -3459,8 +3896,14 @@
       <c r="K32" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L32" s="11">
+        <v>53994</v>
+      </c>
+      <c r="M32" s="11">
+        <v>161982</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>647</v>
       </c>
@@ -3494,8 +3937,10 @@
       <c r="K33" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>147</v>
       </c>
@@ -3529,8 +3974,10 @@
       <c r="K34" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>151</v>
       </c>
@@ -3564,8 +4011,14 @@
       <c r="K35" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L35" s="11">
+        <v>53994</v>
+      </c>
+      <c r="M35" s="11">
+        <v>161982</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>155</v>
       </c>
@@ -3599,8 +4052,10 @@
       <c r="K36" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>159</v>
       </c>
@@ -3634,8 +4089,14 @@
       <c r="K37" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L37" s="11">
+        <v>53994</v>
+      </c>
+      <c r="M37" s="11">
+        <v>161982</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>164</v>
       </c>
@@ -3669,8 +4130,10 @@
       <c r="K38" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>168</v>
       </c>
@@ -3704,8 +4167,10 @@
       <c r="K39" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>172</v>
       </c>
@@ -3739,8 +4204,14 @@
       <c r="K40" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L40" s="11">
+        <v>53994</v>
+      </c>
+      <c r="M40" s="11">
+        <v>161982</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>176</v>
       </c>
@@ -3774,8 +4245,10 @@
       <c r="K41" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L41" s="11"/>
+      <c r="M41" s="11"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>180</v>
       </c>
@@ -3809,8 +4282,14 @@
       <c r="K42" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L42" s="11">
+        <v>53994</v>
+      </c>
+      <c r="M42" s="11">
+        <v>161982</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>185</v>
       </c>
@@ -3844,8 +4323,14 @@
       <c r="K43" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L43" s="11">
+        <v>67980</v>
+      </c>
+      <c r="M43" s="11">
+        <v>203850</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>190</v>
       </c>
@@ -3879,8 +4364,10 @@
       <c r="K44" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L44" s="11"/>
+      <c r="M44" s="11"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>195</v>
       </c>
@@ -3912,8 +4399,10 @@
       <c r="K45" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L45" s="11"/>
+      <c r="M45" s="11"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>199</v>
       </c>
@@ -3947,8 +4436,10 @@
       <c r="K46" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>203</v>
       </c>
@@ -3982,8 +4473,10 @@
       <c r="K47" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L47" s="11"/>
+      <c r="M47" s="11"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>207</v>
       </c>
@@ -4017,8 +4510,10 @@
       <c r="K48" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L48" s="11"/>
+      <c r="M48" s="11"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>212</v>
       </c>
@@ -4052,8 +4547,10 @@
       <c r="K49" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L49" s="11"/>
+      <c r="M49" s="11"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>216</v>
       </c>
@@ -4087,8 +4584,10 @@
       <c r="K50" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L50" s="11"/>
+      <c r="M50" s="11"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>220</v>
       </c>
@@ -4122,8 +4621,10 @@
       <c r="K51" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L51" s="11"/>
+      <c r="M51" s="11"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>225</v>
       </c>
@@ -4157,8 +4658,10 @@
       <c r="K52" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L52" s="11"/>
+      <c r="M52" s="11"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>229</v>
       </c>
@@ -4192,8 +4695,10 @@
       <c r="K53" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L53" s="11"/>
+      <c r="M53" s="11"/>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>234</v>
       </c>
@@ -4227,8 +4732,10 @@
       <c r="K54" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L54" s="11"/>
+      <c r="M54" s="11"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>238</v>
       </c>
@@ -4260,8 +4767,10 @@
       <c r="K55" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L55" s="11"/>
+      <c r="M55" s="11"/>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>242</v>
       </c>
@@ -4291,8 +4800,10 @@
       <c r="K56" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L56" s="11"/>
+      <c r="M56" s="11"/>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>245</v>
       </c>
@@ -4322,8 +4833,10 @@
       <c r="K57" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L57" s="11"/>
+      <c r="M57" s="11"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>248</v>
       </c>
@@ -4353,8 +4866,10 @@
       <c r="K58" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L58" s="11"/>
+      <c r="M58" s="11"/>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>251</v>
       </c>
@@ -4384,8 +4899,10 @@
       <c r="K59" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L59" s="11"/>
+      <c r="M59" s="11"/>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>254</v>
       </c>
@@ -4415,8 +4932,10 @@
       <c r="K60" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L60" s="11"/>
+      <c r="M60" s="11"/>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>257</v>
       </c>
@@ -4446,8 +4965,10 @@
       <c r="K61" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L61" s="11"/>
+      <c r="M61" s="11"/>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>260</v>
       </c>
@@ -4477,8 +4998,10 @@
       <c r="K62" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L62" s="11"/>
+      <c r="M62" s="11"/>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>263</v>
       </c>
@@ -4508,8 +5031,10 @@
       <c r="K63" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L63" s="11"/>
+      <c r="M63" s="11"/>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>266</v>
       </c>
@@ -4539,8 +5064,10 @@
       <c r="K64" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L64" s="11"/>
+      <c r="M64" s="11"/>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>269</v>
       </c>
@@ -4570,8 +5097,10 @@
       <c r="K65" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L65" s="11"/>
+      <c r="M65" s="11"/>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>272</v>
       </c>
@@ -4601,8 +5130,10 @@
       <c r="K66" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L66" s="11"/>
+      <c r="M66" s="11"/>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>275</v>
       </c>
@@ -4632,8 +5163,10 @@
       <c r="K67" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L67" s="11"/>
+      <c r="M67" s="11"/>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>278</v>
       </c>
@@ -4663,8 +5196,10 @@
       <c r="K68" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L68" s="11"/>
+      <c r="M68" s="11"/>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>281</v>
       </c>
@@ -4694,8 +5229,10 @@
       <c r="K69" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L69" s="11"/>
+      <c r="M69" s="11"/>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>284</v>
       </c>
@@ -4725,8 +5262,10 @@
       <c r="K70" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>287</v>
       </c>
@@ -4756,8 +5295,10 @@
       <c r="K71" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L71" s="11"/>
+      <c r="M71" s="11"/>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>290</v>
       </c>
@@ -4787,8 +5328,10 @@
       <c r="K72" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L72" s="11"/>
+      <c r="M72" s="11"/>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>293</v>
       </c>
@@ -4818,8 +5361,10 @@
       <c r="K73" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L73" s="11"/>
+      <c r="M73" s="11"/>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>296</v>
       </c>
@@ -4849,8 +5394,10 @@
       <c r="K74" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L74" s="11"/>
+      <c r="M74" s="11"/>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>299</v>
       </c>
@@ -4884,8 +5431,10 @@
       <c r="K75" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L75" s="11"/>
+      <c r="M75" s="11"/>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>304</v>
       </c>
@@ -4919,8 +5468,10 @@
       <c r="K76" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L76" s="11"/>
+      <c r="M76" s="11"/>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>307</v>
       </c>
@@ -4954,8 +5505,10 @@
       <c r="K77" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L77" s="11"/>
+      <c r="M77" s="11"/>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>310</v>
       </c>
@@ -4989,8 +5542,10 @@
       <c r="K78" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L78" s="11"/>
+      <c r="M78" s="11"/>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>313</v>
       </c>
@@ -5024,8 +5579,10 @@
       <c r="K79" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L79" s="11"/>
+      <c r="M79" s="11"/>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>317</v>
       </c>
@@ -5059,8 +5616,10 @@
       <c r="K80" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L80" s="11"/>
+      <c r="M80" s="11"/>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>320</v>
       </c>
@@ -5094,8 +5653,10 @@
       <c r="K81" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L81" s="11"/>
+      <c r="M81" s="11"/>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>323</v>
       </c>
@@ -5129,8 +5690,10 @@
       <c r="K82" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L82" s="11"/>
+      <c r="M82" s="11"/>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>326</v>
       </c>
@@ -5164,8 +5727,10 @@
       <c r="K83" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L83" s="11"/>
+      <c r="M83" s="11"/>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>329</v>
       </c>
@@ -5199,8 +5764,10 @@
       <c r="K84" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L84" s="11"/>
+      <c r="M84" s="11"/>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>332</v>
       </c>
@@ -5234,8 +5801,14 @@
       <c r="K85" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L85" s="11">
+        <v>53994</v>
+      </c>
+      <c r="M85" s="11">
+        <v>161982</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>335</v>
       </c>
@@ -5269,8 +5842,14 @@
       <c r="K86" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L86" s="11">
+        <v>53994</v>
+      </c>
+      <c r="M86" s="11">
+        <v>161982</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>338</v>
       </c>
@@ -5304,8 +5883,14 @@
       <c r="K87" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L87" s="11">
+        <v>53994</v>
+      </c>
+      <c r="M87" s="11">
+        <v>161982</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>341</v>
       </c>
@@ -5339,8 +5924,10 @@
       <c r="K88" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L88" s="11"/>
+      <c r="M88" s="11"/>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>344</v>
       </c>
@@ -5374,8 +5961,14 @@
       <c r="K89" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L89" s="11">
+        <v>53994</v>
+      </c>
+      <c r="M89" s="11">
+        <v>161982</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>347</v>
       </c>
@@ -5409,8 +6002,10 @@
       <c r="K90" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L90" s="11"/>
+      <c r="M90" s="11"/>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>350</v>
       </c>
@@ -5444,8 +6039,14 @@
       <c r="K91" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L91" s="11">
+        <v>53994</v>
+      </c>
+      <c r="M91" s="11">
+        <v>161982</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>353</v>
       </c>
@@ -5479,8 +6080,10 @@
       <c r="K92" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L92" s="11"/>
+      <c r="M92" s="11"/>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>356</v>
       </c>
@@ -5514,8 +6117,10 @@
       <c r="K93" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L93" s="11"/>
+      <c r="M93" s="11"/>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>359</v>
       </c>
@@ -5549,8 +6154,10 @@
       <c r="K94" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L94" s="11"/>
+      <c r="M94" s="11"/>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>362</v>
       </c>
@@ -5584,8 +6191,10 @@
       <c r="K95" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L95" s="11"/>
+      <c r="M95" s="11"/>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>365</v>
       </c>
@@ -5619,8 +6228,14 @@
       <c r="K96" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L96" s="11">
+        <v>53994</v>
+      </c>
+      <c r="M96" s="11">
+        <v>161982</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>371</v>
       </c>
@@ -5654,8 +6269,14 @@
       <c r="K97" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L97" s="11">
+        <v>53994</v>
+      </c>
+      <c r="M97" s="11">
+        <v>161982</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>374</v>
       </c>
@@ -5689,8 +6310,10 @@
       <c r="K98" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L98" s="11"/>
+      <c r="M98" s="11"/>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>378</v>
       </c>
@@ -5724,8 +6347,10 @@
       <c r="K99" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L99" s="11"/>
+      <c r="M99" s="11"/>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>381</v>
       </c>
@@ -5759,8 +6384,10 @@
       <c r="K100" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L100" s="11"/>
+      <c r="M100" s="11"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>384</v>
       </c>
@@ -5792,8 +6419,10 @@
       <c r="K101" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L101" s="11"/>
+      <c r="M101" s="11"/>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>387</v>
       </c>
@@ -5825,8 +6454,10 @@
       <c r="K102" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L102" s="11"/>
+      <c r="M102" s="11"/>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>390</v>
       </c>
@@ -5860,8 +6491,10 @@
       <c r="K103" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L103" s="11"/>
+      <c r="M103" s="11"/>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>393</v>
       </c>
@@ -5895,8 +6528,10 @@
       <c r="K104" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L104" s="11"/>
+      <c r="M104" s="11"/>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>396</v>
       </c>
@@ -5930,8 +6565,10 @@
       <c r="K105" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L105" s="11"/>
+      <c r="M105" s="11"/>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>399</v>
       </c>
@@ -5965,8 +6602,10 @@
       <c r="K106" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L106" s="11"/>
+      <c r="M106" s="11"/>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>405</v>
       </c>
@@ -6000,8 +6639,10 @@
       <c r="K107" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L107" s="11"/>
+      <c r="M107" s="11"/>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>408</v>
       </c>
@@ -6035,8 +6676,10 @@
       <c r="K108" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L108" s="11"/>
+      <c r="M108" s="11"/>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>411</v>
       </c>
@@ -6070,8 +6713,10 @@
       <c r="K109" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L109" s="11"/>
+      <c r="M109" s="11"/>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>414</v>
       </c>
@@ -6103,8 +6748,10 @@
       <c r="K110" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L110" s="11"/>
+      <c r="M110" s="11"/>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>417</v>
       </c>
@@ -6138,8 +6785,10 @@
       <c r="K111" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L111" s="11"/>
+      <c r="M111" s="11"/>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>422</v>
       </c>
@@ -6173,8 +6822,10 @@
       <c r="K112" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L112" s="11"/>
+      <c r="M112" s="11"/>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>425</v>
       </c>
@@ -6208,8 +6859,14 @@
       <c r="K113" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L113" s="11">
+        <v>57299</v>
+      </c>
+      <c r="M113" s="11">
+        <v>171896</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>429</v>
       </c>
@@ -6243,8 +6900,10 @@
       <c r="K114" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L114" s="11"/>
+      <c r="M114" s="11"/>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>432</v>
       </c>
@@ -6278,8 +6937,10 @@
       <c r="K115" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L115" s="11"/>
+      <c r="M115" s="11"/>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>435</v>
       </c>
@@ -6313,8 +6974,10 @@
       <c r="K116" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L116" s="11"/>
+      <c r="M116" s="11"/>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>438</v>
       </c>
@@ -6348,8 +7011,10 @@
       <c r="K117" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L117" s="11"/>
+      <c r="M117" s="11"/>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>441</v>
       </c>
@@ -6383,8 +7048,10 @@
       <c r="K118" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L118" s="11"/>
+      <c r="M118" s="11"/>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>444</v>
       </c>
@@ -6418,8 +7085,10 @@
       <c r="K119" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L119" s="11"/>
+      <c r="M119" s="11"/>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>447</v>
       </c>
@@ -6453,8 +7122,14 @@
       <c r="K120" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L120" s="11">
+        <v>67900</v>
+      </c>
+      <c r="M120" s="11">
+        <v>203700</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>452</v>
       </c>
@@ -6488,8 +7163,14 @@
       <c r="K121" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L121" s="11">
+        <v>53994</v>
+      </c>
+      <c r="M121" s="11">
+        <v>161982</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>455</v>
       </c>
@@ -6523,8 +7204,10 @@
       <c r="K122" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L122" s="11"/>
+      <c r="M122" s="11"/>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>458</v>
       </c>
@@ -6558,8 +7241,14 @@
       <c r="K123" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L123" s="11">
+        <v>57299</v>
+      </c>
+      <c r="M123" s="11">
+        <v>171896</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>462</v>
       </c>
@@ -6593,8 +7282,14 @@
       <c r="K124" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L124" s="11">
+        <v>63200</v>
+      </c>
+      <c r="M124" s="11">
+        <v>189600</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>466</v>
       </c>
@@ -6628,8 +7323,10 @@
       <c r="K125" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L125" s="11"/>
+      <c r="M125" s="11"/>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>469</v>
       </c>
@@ -6663,8 +7360,10 @@
       <c r="K126" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L126" s="11"/>
+      <c r="M126" s="11"/>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>472</v>
       </c>
@@ -6698,8 +7397,10 @@
       <c r="K127" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L127" s="11"/>
+      <c r="M127" s="11"/>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>475</v>
       </c>
@@ -6733,8 +7434,14 @@
       <c r="K128" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L128" s="11">
+        <v>59700</v>
+      </c>
+      <c r="M128" s="11">
+        <v>179100</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>478</v>
       </c>
@@ -6768,8 +7475,10 @@
       <c r="K129" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L129" s="11"/>
+      <c r="M129" s="11"/>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>481</v>
       </c>
@@ -6801,8 +7510,10 @@
       <c r="K130" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L130" s="11"/>
+      <c r="M130" s="11"/>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>484</v>
       </c>
@@ -6836,8 +7547,10 @@
       <c r="K131" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L131" s="11"/>
+      <c r="M131" s="11"/>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>487</v>
       </c>
@@ -6871,8 +7584,10 @@
       <c r="K132" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L132" s="11"/>
+      <c r="M132" s="11"/>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>490</v>
       </c>
@@ -6906,8 +7621,10 @@
       <c r="K133" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L133" s="11"/>
+      <c r="M133" s="11"/>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>497</v>
       </c>
@@ -6941,8 +7658,10 @@
       <c r="K134" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L134" s="11"/>
+      <c r="M134" s="11"/>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>500</v>
       </c>
@@ -6974,8 +7693,10 @@
       <c r="K135" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L135" s="11"/>
+      <c r="M135" s="11"/>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>505</v>
       </c>
@@ -7009,8 +7730,14 @@
       <c r="K136" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L136" s="11">
+        <v>61900</v>
+      </c>
+      <c r="M136" s="11">
+        <v>185700</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>509</v>
       </c>
@@ -7044,8 +7771,10 @@
       <c r="K137" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L137" s="11"/>
+      <c r="M137" s="11"/>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>513</v>
       </c>
@@ -7079,8 +7808,14 @@
       <c r="K138" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L138" s="11">
+        <v>57299</v>
+      </c>
+      <c r="M138" s="11">
+        <v>171896</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>516</v>
       </c>
@@ -7114,8 +7849,14 @@
       <c r="K139" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L139" s="11">
+        <v>57299</v>
+      </c>
+      <c r="M139" s="11">
+        <v>171896</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>519</v>
       </c>
@@ -7149,8 +7890,10 @@
       <c r="K140" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L140" s="11"/>
+      <c r="M140" s="11"/>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>522</v>
       </c>
@@ -7184,8 +7927,10 @@
       <c r="K141" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L141" s="11"/>
+      <c r="M141" s="11"/>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>525</v>
       </c>
@@ -7219,8 +7964,10 @@
       <c r="K142" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L142" s="11"/>
+      <c r="M142" s="11"/>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>528</v>
       </c>
@@ -7254,8 +8001,10 @@
       <c r="K143" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L143" s="11"/>
+      <c r="M143" s="11"/>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>531</v>
       </c>
@@ -7287,8 +8036,10 @@
       <c r="K144" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L144" s="11"/>
+      <c r="M144" s="11"/>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>534</v>
       </c>
@@ -7320,8 +8071,10 @@
       <c r="K145" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L145" s="11"/>
+      <c r="M145" s="11"/>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>537</v>
       </c>
@@ -7353,8 +8106,10 @@
       <c r="K146" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L146" s="11"/>
+      <c r="M146" s="11"/>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>540</v>
       </c>
@@ -7386,8 +8141,10 @@
       <c r="K147" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L147" s="11"/>
+      <c r="M147" s="11"/>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>543</v>
       </c>
@@ -7421,8 +8178,10 @@
       <c r="K148" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L148" s="11"/>
+      <c r="M148" s="11"/>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>547</v>
       </c>
@@ -7454,8 +8213,14 @@
       <c r="K149" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L149" s="11">
+        <v>73000</v>
+      </c>
+      <c r="M149" s="11">
+        <v>219000</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>553</v>
       </c>
@@ -7487,8 +8252,10 @@
       <c r="K150" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L150" s="11"/>
+      <c r="M150" s="11"/>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>556</v>
       </c>
@@ -7520,8 +8287,14 @@
       <c r="K151" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L151" s="11">
+        <v>69550</v>
+      </c>
+      <c r="M151" s="11">
+        <v>208650</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>559</v>
       </c>
@@ -7553,8 +8326,10 @@
       <c r="K152" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L152" s="11"/>
+      <c r="M152" s="11"/>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>562</v>
       </c>
@@ -7586,8 +8361,14 @@
       <c r="K153" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L153" s="11">
+        <v>57500</v>
+      </c>
+      <c r="M153" s="11">
+        <v>172500</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>565</v>
       </c>
@@ -7619,8 +8400,14 @@
       <c r="K154" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L154" s="11">
+        <v>57299</v>
+      </c>
+      <c r="M154" s="11">
+        <v>171896</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>568</v>
       </c>
@@ -7652,8 +8439,14 @@
       <c r="K155" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L155" s="11">
+        <v>57900</v>
+      </c>
+      <c r="M155" s="11">
+        <v>173700</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>571</v>
       </c>
@@ -7685,8 +8478,14 @@
       <c r="K156" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L156" s="11">
+        <v>61050</v>
+      </c>
+      <c r="M156" s="11">
+        <v>183150</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>574</v>
       </c>
@@ -7718,8 +8517,10 @@
       <c r="K157" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L157" s="11"/>
+      <c r="M157" s="11"/>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>577</v>
       </c>
@@ -7751,8 +8552,14 @@
       <c r="K158" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L158" s="11">
+        <v>57299</v>
+      </c>
+      <c r="M158" s="11">
+        <v>171896</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>580</v>
       </c>
@@ -7784,8 +8591,14 @@
       <c r="K159" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L159" s="11">
+        <v>57299</v>
+      </c>
+      <c r="M159" s="11">
+        <v>171896</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>583</v>
       </c>
@@ -7817,8 +8630,14 @@
       <c r="K160" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L160" s="11">
+        <v>57299</v>
+      </c>
+      <c r="M160" s="11">
+        <v>171896</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>586</v>
       </c>
@@ -7850,8 +8669,10 @@
       <c r="K161" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L161" s="11"/>
+      <c r="M161" s="11"/>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>590</v>
       </c>
@@ -7883,8 +8704,10 @@
       <c r="K162" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L162" s="11"/>
+      <c r="M162" s="11"/>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>593</v>
       </c>
@@ -7916,8 +8739,14 @@
       <c r="K163" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L163" s="11">
+        <v>57299</v>
+      </c>
+      <c r="M163" s="11">
+        <v>171896</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>596</v>
       </c>
@@ -7949,8 +8778,10 @@
       <c r="K164" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L164" s="11"/>
+      <c r="M164" s="11"/>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>599</v>
       </c>
@@ -7982,8 +8813,10 @@
       <c r="K165" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L165" s="11"/>
+      <c r="M165" s="11"/>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>602</v>
       </c>
@@ -8015,8 +8848,10 @@
       <c r="K166" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L166" s="11"/>
+      <c r="M166" s="11"/>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>605</v>
       </c>
@@ -8048,8 +8883,10 @@
       <c r="K167" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L167" s="11"/>
+      <c r="M167" s="11"/>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>608</v>
       </c>
@@ -8081,8 +8918,10 @@
       <c r="K168" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L168" s="11"/>
+      <c r="M168" s="11"/>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>611</v>
       </c>
@@ -8114,8 +8953,10 @@
       <c r="K169" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L169" s="11"/>
+      <c r="M169" s="11"/>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>614</v>
       </c>
@@ -8147,8 +8988,10 @@
       <c r="K170" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L170" s="11"/>
+      <c r="M170" s="11"/>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>617</v>
       </c>
@@ -8180,8 +9023,10 @@
       <c r="K171" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L171" s="11"/>
+      <c r="M171" s="11"/>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>620</v>
       </c>
@@ -8213,8 +9058,10 @@
       <c r="K172" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L172" s="11"/>
+      <c r="M172" s="11"/>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>623</v>
       </c>
@@ -8246,8 +9093,10 @@
       <c r="K173" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L173" s="11"/>
+      <c r="M173" s="11"/>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>626</v>
       </c>
@@ -8279,8 +9128,10 @@
       <c r="K174" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L174" s="11"/>
+      <c r="M174" s="11"/>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>629</v>
       </c>
@@ -8312,8 +9163,10 @@
       <c r="K175" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L175" s="11"/>
+      <c r="M175" s="11"/>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>632</v>
       </c>
@@ -8345,8 +9198,10 @@
       <c r="K176" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L176" s="11"/>
+      <c r="M176" s="11"/>
+    </row>
+    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>635</v>
       </c>
@@ -8378,8 +9233,10 @@
       <c r="K177" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L177" s="11"/>
+      <c r="M177" s="11"/>
+    </row>
+    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>638</v>
       </c>
@@ -8411,8 +9268,10 @@
       <c r="K178" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L178" s="11"/>
+      <c r="M178" s="11"/>
+    </row>
+    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>641</v>
       </c>
@@ -8444,8 +9303,10 @@
       <c r="K179" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L179" s="11"/>
+      <c r="M179" s="11"/>
+    </row>
+    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>644</v>
       </c>
@@ -8477,8 +9338,10 @@
       <c r="K180" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L180" s="11"/>
+      <c r="M180" s="11"/>
+    </row>
+    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>649</v>
       </c>
@@ -8504,14 +9367,1035 @@
       <c r="J181" t="s">
         <v>451</v>
       </c>
+      <c r="L181" s="11"/>
+      <c r="M181" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K181" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B4E39AC-62D1-4699-A8CF-93FD86217211}">
+  <dimension ref="A1:E61"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="17.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>654</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>656</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="8"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+    </row>
+    <row r="3" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
+        <v>658</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C3" s="14">
+        <v>53994</v>
+      </c>
+      <c r="D3" s="14">
+        <v>161982</v>
+      </c>
+      <c r="E3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
+        <v>660</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C4" s="14">
+        <v>53994</v>
+      </c>
+      <c r="D4" s="14">
+        <v>161982</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
+        <v>661</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C5" s="14">
+        <v>67980</v>
+      </c>
+      <c r="D5" s="14">
+        <v>203850</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
+        <v>662</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C6" s="14">
+        <v>53994</v>
+      </c>
+      <c r="D6" s="14">
+        <v>161982</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
+        <v>663</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C7" s="14">
+        <v>80000</v>
+      </c>
+      <c r="D7" s="14">
+        <v>240000</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
+        <v>664</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C8" s="14">
+        <v>72000</v>
+      </c>
+      <c r="D8" s="14">
+        <v>216000</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
+        <v>665</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C9" s="14">
+        <v>100000</v>
+      </c>
+      <c r="D9" s="14">
+        <v>300000</v>
+      </c>
+      <c r="E9" s="11"/>
+    </row>
+    <row r="10" spans="1:5" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
+        <v>666</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C10" s="14">
+        <v>54700</v>
+      </c>
+      <c r="D10" s="14">
+        <v>164100</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="s">
+        <v>667</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C11" s="14">
+        <v>53994</v>
+      </c>
+      <c r="D11" s="14">
+        <v>161982</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="12" t="s">
+        <v>668</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C12" s="14">
+        <v>53994</v>
+      </c>
+      <c r="D12" s="14">
+        <v>161982</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C13" s="14">
+        <v>76000</v>
+      </c>
+      <c r="D13" s="14">
+        <v>228000</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C14" s="14">
+        <v>53994</v>
+      </c>
+      <c r="D14" s="14">
+        <v>161982</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="12" t="s">
+        <v>671</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C15" s="14">
+        <v>55550</v>
+      </c>
+      <c r="D15" s="14">
+        <v>166650</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="12" t="s">
+        <v>672</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C16" s="14">
+        <v>90000</v>
+      </c>
+      <c r="D16" s="14">
+        <v>270000</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C17" s="14">
+        <v>53994</v>
+      </c>
+      <c r="D17" s="14">
+        <v>161982</v>
+      </c>
+      <c r="E17" s="11"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="12" t="s">
+        <v>674</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C18" s="14">
+        <v>80000</v>
+      </c>
+      <c r="D18" s="14">
+        <v>240000</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A19" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C19" s="14">
+        <v>80000</v>
+      </c>
+      <c r="D19" s="14">
+        <v>240000</v>
+      </c>
+      <c r="E19" s="11"/>
+    </row>
+    <row r="20" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A20" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C20" s="14">
+        <v>53994</v>
+      </c>
+      <c r="D20" s="14">
+        <v>161982</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="12" t="s">
+        <v>677</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C21" s="14">
+        <v>53994</v>
+      </c>
+      <c r="D21" s="14">
+        <v>161982</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A22" s="12" t="s">
+        <v>678</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C22" s="14">
+        <v>53994</v>
+      </c>
+      <c r="D22" s="14">
+        <v>161982</v>
+      </c>
+      <c r="E22" s="11"/>
+    </row>
+    <row r="23" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A23" s="12" t="s">
+        <v>679</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C23" s="14">
+        <v>53994</v>
+      </c>
+      <c r="D23" s="14">
+        <v>161982</v>
+      </c>
+      <c r="E23" s="11"/>
+    </row>
+    <row r="24" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A24" s="12" t="s">
+        <v>680</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C24" s="14">
+        <v>59700</v>
+      </c>
+      <c r="D24" s="14">
+        <v>179100</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A25" s="12" t="s">
+        <v>681</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C25" s="14">
+        <v>53994</v>
+      </c>
+      <c r="D25" s="14">
+        <v>161982</v>
+      </c>
+      <c r="E25" s="11"/>
+    </row>
+    <row r="26" spans="1:5" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="12" t="s">
+        <v>682</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C26" s="14">
+        <v>56300</v>
+      </c>
+      <c r="D26" s="14">
+        <v>168900</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="12" t="s">
+        <v>683</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C27" s="14">
+        <v>53994</v>
+      </c>
+      <c r="D27" s="14">
+        <v>161982</v>
+      </c>
+      <c r="E27" s="11"/>
+    </row>
+    <row r="28" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A28" s="12" t="s">
+        <v>684</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C28" s="14">
+        <v>53994</v>
+      </c>
+      <c r="D28" s="14">
+        <v>161982</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A29" s="12" t="s">
+        <v>685</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C29" s="14">
+        <v>53994</v>
+      </c>
+      <c r="D29" s="14">
+        <v>161982</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A30" s="12" t="s">
+        <v>686</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C30" s="14">
+        <v>63500</v>
+      </c>
+      <c r="D30" s="14">
+        <v>190500</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A31" s="12" t="s">
+        <v>687</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C31" s="14">
+        <v>66300</v>
+      </c>
+      <c r="D31" s="14">
+        <v>198900</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C32" s="14">
+        <v>53994</v>
+      </c>
+      <c r="D32" s="14">
+        <v>161982</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="12" t="s">
+        <v>688</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C33" s="14">
+        <v>58000</v>
+      </c>
+      <c r="D33" s="14">
+        <v>174000</v>
+      </c>
+      <c r="E33" s="11"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="12" t="s">
+        <v>689</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C34" s="14">
+        <v>53994</v>
+      </c>
+      <c r="D34" s="14">
+        <v>161982</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A35" s="12" t="s">
+        <v>690</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C35" s="14">
+        <v>53994</v>
+      </c>
+      <c r="D35" s="14">
+        <v>161982</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="12" t="s">
+        <v>691</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C36" s="14">
+        <v>64900</v>
+      </c>
+      <c r="D36" s="14">
+        <v>194700</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="12" t="s">
+        <v>692</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C37" s="14">
+        <v>53994</v>
+      </c>
+      <c r="D37" s="14">
+        <v>161982</v>
+      </c>
+      <c r="E37" s="11"/>
+    </row>
+    <row r="38" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A38" s="12" t="s">
+        <v>693</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C38" s="14">
+        <v>76750</v>
+      </c>
+      <c r="D38" s="14">
+        <v>230250</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A39" s="12" t="s">
+        <v>694</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C39" s="14">
+        <v>53994</v>
+      </c>
+      <c r="D39" s="14">
+        <v>161982</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="30.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="12" t="s">
+        <v>695</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C40" s="14">
+        <v>65000</v>
+      </c>
+      <c r="D40" s="14">
+        <v>195000</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A41" s="12" t="s">
+        <v>696</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="C41" s="14">
+        <v>53994</v>
+      </c>
+      <c r="D41" s="14">
+        <v>161982</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="17" t="s">
+        <v>697</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>698</v>
+      </c>
+      <c r="C42" s="16">
+        <v>57299</v>
+      </c>
+      <c r="D42" s="16">
+        <v>171896</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="18" t="s">
+        <v>699</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>698</v>
+      </c>
+      <c r="C43" s="16">
+        <v>57299</v>
+      </c>
+      <c r="D43" s="16">
+        <v>171896</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="18" t="s">
+        <v>700</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>698</v>
+      </c>
+      <c r="C44" s="16">
+        <v>57299</v>
+      </c>
+      <c r="D44" s="16">
+        <v>171896</v>
+      </c>
+      <c r="E44" s="11"/>
+    </row>
+    <row r="45" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="18" t="s">
+        <v>701</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>698</v>
+      </c>
+      <c r="C45" s="14">
+        <v>73000</v>
+      </c>
+      <c r="D45" s="14">
+        <v>219000</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="18" t="s">
+        <v>702</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>698</v>
+      </c>
+      <c r="C46" s="14">
+        <v>57299</v>
+      </c>
+      <c r="D46" s="14">
+        <v>171896</v>
+      </c>
+      <c r="E46" s="11"/>
+    </row>
+    <row r="47" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="18" t="s">
+        <v>703</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>698</v>
+      </c>
+      <c r="C47" s="14">
+        <v>57299</v>
+      </c>
+      <c r="D47" s="14">
+        <v>171896</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="18" t="s">
+        <v>704</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>698</v>
+      </c>
+      <c r="C48" s="14">
+        <v>57299</v>
+      </c>
+      <c r="D48" s="14">
+        <v>171896</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="18" t="s">
+        <v>705</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>698</v>
+      </c>
+      <c r="C49" s="14">
+        <v>61050</v>
+      </c>
+      <c r="D49" s="14">
+        <v>183150</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="18" t="s">
+        <v>706</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>698</v>
+      </c>
+      <c r="C50" s="14">
+        <v>63200</v>
+      </c>
+      <c r="D50" s="14">
+        <v>189600</v>
+      </c>
+      <c r="E50" s="11" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="31.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="18" t="s">
+        <v>707</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>698</v>
+      </c>
+      <c r="C51" s="14">
+        <v>67900</v>
+      </c>
+      <c r="D51" s="14">
+        <v>203700</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="31.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="18" t="s">
+        <v>708</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>698</v>
+      </c>
+      <c r="C52" s="14">
+        <v>53994</v>
+      </c>
+      <c r="D52" s="14">
+        <v>161982</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="18" t="s">
+        <v>709</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>698</v>
+      </c>
+      <c r="C53" s="14">
+        <v>61900</v>
+      </c>
+      <c r="D53" s="14">
+        <v>185700</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="18" t="s">
+        <v>710</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>698</v>
+      </c>
+      <c r="C54" s="14">
+        <v>57299</v>
+      </c>
+      <c r="D54" s="14">
+        <v>171896</v>
+      </c>
+      <c r="E54" s="11"/>
+    </row>
+    <row r="55" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A55" s="18" t="s">
+        <v>711</v>
+      </c>
+      <c r="B55" s="13" t="s">
+        <v>698</v>
+      </c>
+      <c r="C55" s="14">
+        <v>57299</v>
+      </c>
+      <c r="D55" s="14">
+        <v>171896</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A56" s="18" t="s">
+        <v>712</v>
+      </c>
+      <c r="B56" s="13" t="s">
+        <v>698</v>
+      </c>
+      <c r="C56" s="14">
+        <v>57299</v>
+      </c>
+      <c r="D56" s="14">
+        <v>171896</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="B57" s="13" t="s">
+        <v>698</v>
+      </c>
+      <c r="C57" s="14">
+        <v>57500</v>
+      </c>
+      <c r="D57" s="14">
+        <v>172500</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A58" s="18" t="s">
+        <v>714</v>
+      </c>
+      <c r="B58" s="13" t="s">
+        <v>698</v>
+      </c>
+      <c r="C58" s="14">
+        <v>57299</v>
+      </c>
+      <c r="D58" s="14">
+        <v>171896</v>
+      </c>
+      <c r="E58" s="11" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A59" s="18" t="s">
+        <v>715</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>698</v>
+      </c>
+      <c r="C59" s="14">
+        <v>57299</v>
+      </c>
+      <c r="D59" s="14">
+        <v>171896</v>
+      </c>
+      <c r="E59" s="11" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A60" s="18" t="s">
+        <v>716</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>698</v>
+      </c>
+      <c r="C60" s="14">
+        <v>69550</v>
+      </c>
+      <c r="D60" s="14">
+        <v>208650</v>
+      </c>
+      <c r="E60" s="11" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="21.6" x14ac:dyDescent="0.3">
+      <c r="A61" s="18" t="s">
+        <v>717</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>698</v>
+      </c>
+      <c r="C61" s="14">
+        <v>57900</v>
+      </c>
+      <c r="D61" s="14">
+        <v>173700</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>570</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A1:A2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
